--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h4.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h4.xlsx
@@ -459,31 +459,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D2">
-        <v>0.5381470199549665</v>
+        <v>0.3835455452147749</v>
       </c>
       <c r="E2">
         <v>2.507941123023818</v>
       </c>
       <c r="F2">
-        <v>2.646088142978778</v>
+        <v>2.491486668238587</v>
       </c>
       <c r="G2">
-        <v>-0.1381470199549608</v>
+        <v>0.01645445478523078</v>
       </c>
       <c r="H2">
-        <v>0.1381470199549608</v>
+        <v>-0.01645445478523078</v>
       </c>
       <c r="I2">
-        <v>0.7120137838589127</v>
+        <v>-0.08226285854335291</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -497,22 +497,22 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D3">
-        <v>0.5428404592108562</v>
+        <v>0.4536132983556092</v>
       </c>
       <c r="E3">
         <v>-0.01752140864044649</v>
       </c>
       <c r="F3">
-        <v>0.2253190505704268</v>
+        <v>0.1360918897151798</v>
       </c>
       <c r="G3">
-        <v>-0.2428404592108733</v>
+        <v>-0.1536132983556263</v>
       </c>
       <c r="H3">
-        <v>0.2077976419299803</v>
+        <v>0.1185704810747333</v>
       </c>
       <c r="I3">
-        <v>0.05046167478921305</v>
+        <v>0.01821400268550315</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -535,22 +535,22 @@
         <v>-0.2499999999999858</v>
       </c>
       <c r="D4">
-        <v>0.5304270156820091</v>
+        <v>0.3508994068095047</v>
       </c>
       <c r="E4">
         <v>-0.2595084149472189</v>
       </c>
       <c r="F4">
-        <v>0.5209186007347759</v>
+        <v>0.3413909918622716</v>
       </c>
       <c r="G4">
-        <v>-0.7804270156819949</v>
+        <v>-0.6008994068094905</v>
       </c>
       <c r="H4">
-        <v>0.261410185787557</v>
+        <v>0.08188257691505263</v>
       </c>
       <c r="I4">
-        <v>0.2040115711630589</v>
+        <v>0.04920319189628761</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -573,31 +573,31 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.4670057377084493</v>
+        <v>-3.449051755073842</v>
       </c>
       <c r="E5">
         <v>-2.182091798344627</v>
       </c>
       <c r="F5">
-        <v>-1.715086060636178</v>
+        <v>-5.631143553418469</v>
       </c>
       <c r="G5">
-        <v>-0.4670057377084493</v>
+        <v>3.449051755073842</v>
       </c>
       <c r="H5">
-        <v>-0.4670057377084493</v>
+        <v>3.449051755073842</v>
       </c>
       <c r="I5">
-        <v>-1.820004421014366</v>
+        <v>26.94825310280349</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -611,28 +611,28 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D6">
-        <v>0.4869295220551066</v>
+        <v>0.2600239868695283</v>
       </c>
       <c r="E6">
         <v>-0.06479708162335629</v>
       </c>
       <c r="F6">
-        <v>0.1221324404317674</v>
+        <v>-0.1047730947538109</v>
       </c>
       <c r="G6">
-        <v>-0.1869295220551237</v>
+        <v>0.03997601313045457</v>
       </c>
       <c r="H6">
-        <v>0.05733535880841112</v>
+        <v>0.03997601313045457</v>
       </c>
       <c r="I6">
-        <v>0.01071767121891532</v>
+        <v>0.006778739597387132</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -649,31 +649,31 @@
         <v>0.3250000000000028</v>
       </c>
       <c r="D7">
-        <v>0.4821135964313792</v>
+        <v>0.2104081229119797</v>
       </c>
       <c r="E7">
         <v>0.2057776962582608</v>
       </c>
       <c r="F7">
-        <v>0.3628912926896372</v>
+        <v>0.09118581917023769</v>
       </c>
       <c r="G7">
-        <v>-0.1571135964313764</v>
+        <v>0.1145918770880231</v>
       </c>
       <c r="H7">
-        <v>0.1571135964313764</v>
+        <v>-0.1145918770880231</v>
       </c>
       <c r="I7">
-        <v>0.08934563003259888</v>
+        <v>-0.03402960665960975</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -687,31 +687,31 @@
         <v>0.5</v>
       </c>
       <c r="D8">
-        <v>0.5013923898995322</v>
+        <v>0.3221748105733957</v>
       </c>
       <c r="E8">
         <v>0.6818677821223996</v>
       </c>
       <c r="F8">
-        <v>0.6832601720219318</v>
+        <v>0.5040425926957953</v>
       </c>
       <c r="G8">
-        <v>-0.001392389899532165</v>
+        <v>0.1778251894266043</v>
       </c>
       <c r="H8">
-        <v>0.001392389899532165</v>
+        <v>-0.1778251894266043</v>
       </c>
       <c r="I8">
-        <v>0.001900790374919581</v>
+        <v>-0.2108847370450208</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -725,22 +725,22 @@
         <v>0.6</v>
       </c>
       <c r="D9">
-        <v>0.5071152296311063</v>
+        <v>0.3484291940412945</v>
       </c>
       <c r="E9">
         <v>0.3292907417433573</v>
       </c>
       <c r="F9">
-        <v>0.2364059713744636</v>
+        <v>0.07771993578465181</v>
       </c>
       <c r="G9">
-        <v>0.09288477036889364</v>
+        <v>0.2515708059587055</v>
       </c>
       <c r="H9">
-        <v>-0.09288477036889364</v>
+        <v>-0.2515708059587055</v>
       </c>
       <c r="I9">
-        <v>-0.05254460929638669</v>
+        <v>-0.10239200417952</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -763,22 +763,22 @@
         <v>0.3</v>
       </c>
       <c r="D10">
-        <v>0.4987597405659239</v>
+        <v>0.3143501320039255</v>
       </c>
       <c r="E10">
         <v>0.8925127928898435</v>
       </c>
       <c r="F10">
-        <v>1.091272533455767</v>
+        <v>0.906862924893769</v>
       </c>
       <c r="G10">
-        <v>-0.1987597405659239</v>
+        <v>-0.01435013200392549</v>
       </c>
       <c r="H10">
-        <v>0.1987597405659238</v>
+        <v>0.01435013200392543</v>
       </c>
       <c r="I10">
-        <v>0.3942966568029402</v>
+        <v>0.02582127907485299</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -801,31 +801,31 @@
         <v>0.4</v>
       </c>
       <c r="D11">
-        <v>0.4949072544983888</v>
+        <v>0.2814140383200912</v>
       </c>
       <c r="E11">
         <v>-0.3214356569573426</v>
       </c>
       <c r="F11">
-        <v>-0.2265284024589538</v>
+        <v>-0.4400216186372514</v>
       </c>
       <c r="G11">
-        <v>-0.09490725449838877</v>
+        <v>0.1185859616799088</v>
       </c>
       <c r="H11">
-        <v>-0.09490725449838877</v>
+        <v>0.1185859616799088</v>
       </c>
       <c r="I11">
-        <v>-0.05200576444299265</v>
+        <v>0.09029814330454827</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,25 +839,25 @@
         <v>0.5</v>
       </c>
       <c r="D12">
-        <v>0.4942467537898793</v>
+        <v>0.2917061406327234</v>
       </c>
       <c r="E12">
         <v>0.1162427487728631</v>
       </c>
       <c r="F12">
-        <v>0.1104895025627424</v>
+        <v>-0.09205111059441351</v>
       </c>
       <c r="G12">
-        <v>0.005753246210120688</v>
+        <v>0.2082938593672766</v>
       </c>
       <c r="H12">
-        <v>-0.005753246210120688</v>
+        <v>-0.0241916381784496</v>
       </c>
       <c r="I12">
-        <v>-0.001304446465708703</v>
+        <v>-0.005038969680606022</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -877,31 +877,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D13">
-        <v>0.4836157536718193</v>
+        <v>0.2191744333381033</v>
       </c>
       <c r="E13">
         <v>0.6108782057348251</v>
       </c>
       <c r="F13">
-        <v>0.6444939594066558</v>
+        <v>0.3800526390729398</v>
       </c>
       <c r="G13">
-        <v>-0.03361575367183073</v>
+        <v>0.2308255666618853</v>
       </c>
       <c r="H13">
-        <v>0.03361575367183067</v>
+        <v>-0.2308255666618853</v>
       </c>
       <c r="I13">
-        <v>0.04220028146986876</v>
+        <v>-0.2287321737754931</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -915,22 +915,22 @@
         <v>0.6</v>
       </c>
       <c r="D14">
-        <v>0.4865405690544947</v>
+        <v>0.2858441738424585</v>
       </c>
       <c r="E14">
         <v>-0.09969742813917826</v>
       </c>
       <c r="F14">
-        <v>-0.2131568590846835</v>
+        <v>-0.4138532542967197</v>
       </c>
       <c r="G14">
-        <v>0.1134594309455053</v>
+        <v>0.3141558261575415</v>
       </c>
       <c r="H14">
-        <v>0.1134594309455053</v>
+        <v>0.3141558261575415</v>
       </c>
       <c r="I14">
-        <v>0.03549626939728101</v>
+        <v>0.1613349389144187</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -953,31 +953,31 @@
         <v>0.5200000000000102</v>
       </c>
       <c r="D15">
-        <v>0.4887241460161824</v>
+        <v>0.3326047282185538</v>
       </c>
       <c r="E15">
         <v>0.08136257582828943</v>
       </c>
       <c r="F15">
-        <v>0.05008672184446161</v>
+        <v>-0.106032695953167</v>
       </c>
       <c r="G15">
-        <v>0.03127585398382782</v>
+        <v>0.1873952717814564</v>
       </c>
       <c r="H15">
-        <v>-0.03127585398382782</v>
+        <v>0.02467012012487757</v>
       </c>
       <c r="I15">
-        <v>-0.004111189040289679</v>
+        <v>0.00462306386568261</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -991,31 +991,31 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D16">
-        <v>0.4765140423726502</v>
+        <v>0.2536627374024515</v>
       </c>
       <c r="E16">
         <v>0.151307328824247</v>
       </c>
       <c r="F16">
-        <v>0.2078213711968955</v>
+        <v>-0.01502993377330319</v>
       </c>
       <c r="G16">
-        <v>-0.05651404237264851</v>
+        <v>0.1663372625975502</v>
       </c>
       <c r="H16">
-        <v>0.05651404237264851</v>
+        <v>-0.1362773950509438</v>
       </c>
       <c r="I16">
-        <v>0.02029581457022902</v>
+        <v>-0.02266800884669893</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,28 +1029,28 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D17">
-        <v>0.4778876608539055</v>
+        <v>0.33619737748089</v>
       </c>
       <c r="E17">
         <v>-0.01125936757448054</v>
       </c>
       <c r="F17">
-        <v>0.06662829327941927</v>
+        <v>-0.07506199009359621</v>
       </c>
       <c r="G17">
-        <v>-0.07788766085389981</v>
+        <v>0.06380262251911567</v>
       </c>
       <c r="H17">
-        <v>0.05536892570493873</v>
+        <v>0.06380262251911567</v>
       </c>
       <c r="I17">
-        <v>0.004312556107151043</v>
+        <v>0.005507528998633871</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1067,28 +1067,28 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D18">
-        <v>0.479171576068976</v>
+        <v>0.3216369381519656</v>
       </c>
       <c r="E18">
         <v>0.02207657371243049</v>
       </c>
       <c r="F18">
-        <v>0.05224814978139419</v>
+        <v>-0.1052864881356162</v>
       </c>
       <c r="G18">
-        <v>-0.0301715760689637</v>
+        <v>0.1273630618480467</v>
       </c>
       <c r="H18">
-        <v>0.0301715760689637</v>
+        <v>0.0832099144231857</v>
       </c>
       <c r="I18">
-        <v>0.002242494048698625</v>
+        <v>0.01059786947705087</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         <v>0.4799999999999898</v>
       </c>
       <c r="D19">
-        <v>0.4796550976332909</v>
+        <v>0.3554346767339184</v>
       </c>
       <c r="E19">
         <v>-0.1364567140176977</v>
       </c>
       <c r="F19">
-        <v>-0.1368016163843966</v>
+        <v>-0.2610220372837692</v>
       </c>
       <c r="G19">
-        <v>0.0003449023666989293</v>
+        <v>0.1245653232660714</v>
       </c>
       <c r="H19">
-        <v>0.0003449023666989293</v>
+        <v>0.1245653232660714</v>
       </c>
       <c r="I19">
-        <v>9.424744487588135E-05</v>
+        <v>0.04951206914726164</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -1143,31 +1143,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D20">
-        <v>0.4792588241132884</v>
+        <v>0.3582908186824177</v>
       </c>
       <c r="E20">
         <v>-0.2069669247009072</v>
       </c>
       <c r="F20">
-        <v>-0.1277081005876244</v>
+        <v>-0.2486761060184952</v>
       </c>
       <c r="G20">
-        <v>-0.07925882411328272</v>
+        <v>0.041709181317588</v>
       </c>
       <c r="H20">
-        <v>-0.07925882411328272</v>
+        <v>0.041709181317588</v>
       </c>
       <c r="I20">
-        <v>-0.02652594896445217</v>
+        <v>0.01900449778437087</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,28 +1181,28 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D21">
-        <v>0.4808133254998962</v>
+        <v>0.3962017054427926</v>
       </c>
       <c r="E21">
         <v>-0.00158488927486683</v>
       </c>
       <c r="F21">
-        <v>0.02922843622504079</v>
+        <v>-0.05538318383206281</v>
       </c>
       <c r="G21">
-        <v>-0.03081332549990762</v>
+        <v>0.05379829455719598</v>
       </c>
       <c r="H21">
-        <v>0.02764354695017396</v>
+        <v>0.05379829455719598</v>
       </c>
       <c r="I21">
-        <v>0.0008517896101476887</v>
+        <v>0.003064785177362476</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1219,22 +1219,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D22">
-        <v>0.4882493995579117</v>
+        <v>0.4050833792330935</v>
       </c>
       <c r="E22">
         <v>0.4826764833261045</v>
       </c>
       <c r="F22">
-        <v>0.4709258828840304</v>
+        <v>0.3877598625592121</v>
       </c>
       <c r="G22">
-        <v>0.0117506004420741</v>
+        <v>0.09491662076689228</v>
       </c>
       <c r="H22">
-        <v>-0.0117506004420741</v>
+        <v>-0.09491662076689233</v>
       </c>
       <c r="I22">
-        <v>-0.01120540038595172</v>
+        <v>-0.08261887654411612</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -1257,25 +1257,25 @@
         <v>0.5999999999999943</v>
       </c>
       <c r="D23">
-        <v>0.4880180400406549</v>
+        <v>0.4069313927782377</v>
       </c>
       <c r="E23">
         <v>0.1756473542911566</v>
       </c>
       <c r="F23">
-        <v>0.06366539433181723</v>
+        <v>-0.01742125293059998</v>
       </c>
       <c r="G23">
-        <v>0.1119819599593394</v>
+        <v>0.1930686072217566</v>
       </c>
       <c r="H23">
-        <v>-0.1119819599593394</v>
+        <v>-0.1582261013605566</v>
       </c>
       <c r="I23">
-        <v>-0.02679871063405732</v>
+        <v>-0.03054849301581116</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1295,22 +1295,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D24">
-        <v>0.4862102413152092</v>
+        <v>0.3723580685577372</v>
       </c>
       <c r="E24">
         <v>0.5746895714685679</v>
       </c>
       <c r="F24">
-        <v>0.5608998127837913</v>
+        <v>0.4470476400263193</v>
       </c>
       <c r="G24">
-        <v>0.01378975868477661</v>
+        <v>0.1276419314422486</v>
       </c>
       <c r="H24">
-        <v>-0.01378975868477661</v>
+        <v>-0.1276419314422486</v>
       </c>
       <c r="I24">
-        <v>-0.01565950357383411</v>
+        <v>-0.1304165111016247</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -1333,31 +1333,31 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D25">
-        <v>0.4883606505958775</v>
+        <v>0.3520711141246315</v>
       </c>
       <c r="E25">
         <v>0.3648406583130818</v>
       </c>
       <c r="F25">
-        <v>0.4042013089089471</v>
+        <v>0.267911772437701</v>
       </c>
       <c r="G25">
-        <v>-0.03936065059586524</v>
+        <v>0.09692888587538079</v>
       </c>
       <c r="H25">
-        <v>0.03936065059586524</v>
+        <v>-0.09692888587538079</v>
       </c>
       <c r="I25">
-        <v>0.03026999216538315</v>
+        <v>-0.06133198814761241</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1371,22 +1371,22 @@
         <v>0.3</v>
       </c>
       <c r="D26">
-        <v>0.4833702201414928</v>
+        <v>0.315642269916694</v>
       </c>
       <c r="E26">
         <v>0.2720044792833136</v>
       </c>
       <c r="F26">
-        <v>0.4553746994248064</v>
+        <v>0.2876467492000076</v>
       </c>
       <c r="G26">
-        <v>-0.1833702201414928</v>
+        <v>-0.01564226991669398</v>
       </c>
       <c r="H26">
-        <v>0.1833702201414928</v>
+        <v>0.01564226991669398</v>
       </c>
       <c r="I26">
-        <v>0.1333796801260462</v>
+        <v>0.008754215575145496</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -1409,31 +1409,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D27">
-        <v>0.4810195595070728</v>
+        <v>0.2958996989616331</v>
       </c>
       <c r="E27">
         <v>2.571807318894714</v>
       </c>
       <c r="F27">
-        <v>2.702826878401779</v>
+        <v>2.517707017856339</v>
       </c>
       <c r="G27">
-        <v>-0.1310195595070643</v>
+        <v>0.05410030103837543</v>
       </c>
       <c r="H27">
-        <v>0.1310195595070645</v>
+        <v>-0.0541003010383756</v>
       </c>
       <c r="I27">
-        <v>0.6910802490906853</v>
+        <v>-0.2753442577573599</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1447,22 +1447,22 @@
         <v>0.3</v>
       </c>
       <c r="D28">
-        <v>0.4817835198719557</v>
+        <v>0.3191816656823959</v>
       </c>
       <c r="E28">
         <v>9.990957649752</v>
       </c>
       <c r="F28">
-        <v>10.17274116962395</v>
+        <v>10.0101393154344</v>
       </c>
       <c r="G28">
-        <v>-0.1817835198719557</v>
+        <v>-0.01918166568239593</v>
       </c>
       <c r="H28">
-        <v>0.1817835198719546</v>
+        <v>0.01918166568239599</v>
       </c>
       <c r="I28">
-        <v>3.665428145024137</v>
+        <v>0.3836543552673959</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,31 +1485,31 @@
         <v>0.3490000000000038</v>
       </c>
       <c r="D29">
-        <v>0.4764707641058692</v>
+        <v>0.2907722840070606</v>
       </c>
       <c r="E29">
         <v>-8.131304150385466</v>
       </c>
       <c r="F29">
-        <v>-8.003833386279601</v>
+        <v>-8.18953186637841</v>
       </c>
       <c r="G29">
-        <v>-0.1274707641058654</v>
+        <v>0.05822771599294319</v>
       </c>
       <c r="H29">
-        <v>-0.1274707641058654</v>
+        <v>0.05822771599294363</v>
       </c>
       <c r="I29">
-        <v>-2.056758310751931</v>
+        <v>0.9503250043515266</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1523,28 +1523,28 @@
         <v>0.3400000000000034</v>
       </c>
       <c r="D30">
-        <v>0.473606302763202</v>
+        <v>0.2851414742459503</v>
       </c>
       <c r="E30">
         <v>-0.0006326034063171004</v>
       </c>
       <c r="F30">
-        <v>0.1329736993568815</v>
+        <v>-0.05549112916037019</v>
       </c>
       <c r="G30">
-        <v>-0.1336063027631986</v>
+        <v>0.05485852575405309</v>
       </c>
       <c r="H30">
-        <v>0.1323410959505644</v>
+        <v>0.05485852575405309</v>
       </c>
       <c r="I30">
-        <v>0.01768160453358461</v>
+        <v>0.003078865228423203</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
@@ -1561,22 +1561,22 @@
         <v>1.499999999999986</v>
       </c>
       <c r="D31">
-        <v>0.4723109522325753</v>
+        <v>0.2747159319351871</v>
       </c>
       <c r="E31">
         <v>3.306937868393058</v>
       </c>
       <c r="F31">
-        <v>2.279248820625647</v>
+        <v>2.081653800328259</v>
       </c>
       <c r="G31">
-        <v>1.027689047767411</v>
+        <v>1.225284068064799</v>
       </c>
       <c r="H31">
-        <v>-1.027689047767411</v>
+        <v>-1.225284068064799</v>
       </c>
       <c r="I31">
-        <v>-5.740862879088617</v>
+        <v>-6.602555520990938</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -1599,22 +1599,22 @@
         <v>1.1</v>
       </c>
       <c r="D32">
-        <v>0.4498297512016902</v>
+        <v>0.1243683820346405</v>
       </c>
       <c r="E32">
         <v>-0.5330921181302579</v>
       </c>
       <c r="F32">
-        <v>-1.183262366928568</v>
+        <v>-1.508723736095618</v>
       </c>
       <c r="G32">
-        <v>0.6501702487983099</v>
+        <v>0.9756316179653596</v>
       </c>
       <c r="H32">
-        <v>0.6501702487983099</v>
+        <v>0.9756316179653597</v>
       </c>
       <c r="I32">
-        <v>1.115922622576792</v>
+        <v>1.992060105445714</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -1637,22 +1637,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D33">
-        <v>0.2568851861623672</v>
+        <v>-2.902546736670638</v>
       </c>
       <c r="E33">
         <v>-1.194266296544473</v>
       </c>
       <c r="F33">
-        <v>-1.437381110382092</v>
+        <v>-4.596813033215097</v>
       </c>
       <c r="G33">
-        <v>0.2431148138376186</v>
+        <v>3.402546736670624</v>
       </c>
       <c r="H33">
-        <v>0.2431148138376185</v>
+        <v>3.402546736670624</v>
       </c>
       <c r="I33">
-        <v>0.6397924694212034</v>
+        <v>19.70441807527413</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -1675,25 +1675,25 @@
         <v>0.599752004175059</v>
       </c>
       <c r="D34">
-        <v>0.4144167548794022</v>
+        <v>-0.3734140541957911</v>
       </c>
       <c r="E34">
         <v>0.9469416447868544</v>
       </c>
       <c r="F34">
-        <v>0.7616063954911976</v>
+        <v>-0.02622441358399569</v>
       </c>
       <c r="G34">
-        <v>0.1853352492956568</v>
+        <v>0.9731660583708501</v>
       </c>
       <c r="H34">
-        <v>-0.1853352492956568</v>
+        <v>-0.9207172312028586</v>
       </c>
       <c r="I34">
-        <v>-0.3166541769785386</v>
+        <v>-0.8960107587638086</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -1713,25 +1713,25 @@
         <v>0.48702</v>
       </c>
       <c r="D35">
-        <v>0.4523996308710531</v>
+        <v>0.2326449304998711</v>
       </c>
       <c r="E35">
         <v>0.2516151035781544</v>
       </c>
       <c r="F35">
-        <v>0.2169947344492075</v>
+        <v>-0.0027599659219745</v>
       </c>
       <c r="G35">
-        <v>0.03462036912894689</v>
+        <v>0.2543750695001289</v>
       </c>
       <c r="H35">
-        <v>-0.03462036912894689</v>
+        <v>-0.2488551376561799</v>
       </c>
       <c r="I35">
-        <v>-0.01622344556996329</v>
+        <v>-0.06330254293675493</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>0.4615552350996976</v>
       </c>
       <c r="D36">
-        <v>0.4476827517870831</v>
+        <v>0.3437870769602576</v>
       </c>
       <c r="E36">
         <v>0.3218253794872098</v>
       </c>
       <c r="F36">
-        <v>0.3079528961745953</v>
+        <v>0.2040572213477698</v>
       </c>
       <c r="G36">
-        <v>0.01387248331261448</v>
+        <v>0.11776815813944</v>
       </c>
       <c r="H36">
-        <v>-0.01387248331261448</v>
+        <v>-0.11776815813944</v>
       </c>
       <c r="I36">
-        <v>-0.00873658861976552</v>
+        <v>-0.06193222529791387</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
@@ -1789,25 +1789,25 @@
         <v>0.71</v>
       </c>
       <c r="D37">
-        <v>0.451976512729612</v>
+        <v>0.298809095368558</v>
       </c>
       <c r="E37">
         <v>0.3098511073887893</v>
       </c>
       <c r="F37">
-        <v>0.05182762011840136</v>
+        <v>-0.1013397972426526</v>
       </c>
       <c r="G37">
-        <v>0.258023487270388</v>
+        <v>0.411190904631442</v>
       </c>
       <c r="H37">
-        <v>-0.258023487270388</v>
+        <v>-0.2085113101461367</v>
       </c>
       <c r="I37">
-        <v>-0.09332160654292175</v>
+        <v>-0.08573795424487712</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -1827,22 +1827,22 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="D38">
-        <v>0.4590078131503196</v>
+        <v>0.3513522662197494</v>
       </c>
       <c r="E38">
         <v>1.245306103547281</v>
       </c>
       <c r="F38">
-        <v>0.8943139166976002</v>
+        <v>0.78665836976703</v>
       </c>
       <c r="G38">
-        <v>0.3509921868496805</v>
+        <v>0.4586477337802506</v>
       </c>
       <c r="H38">
-        <v>-0.3509921868496806</v>
+        <v>-0.4586477337802508</v>
       </c>
       <c r="I38">
-        <v>-0.7509899099331087</v>
+        <v>-0.9319559008075896</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
@@ -1865,22 +1865,22 @@
         <v>0.8907665627173156</v>
       </c>
       <c r="D39">
-        <v>0.4613276753353009</v>
+        <v>0.4361238707313746</v>
       </c>
       <c r="E39">
         <v>1.225993306361975</v>
       </c>
       <c r="F39">
-        <v>0.79655441897996</v>
+        <v>0.7713506143760337</v>
       </c>
       <c r="G39">
-        <v>0.4294388873820147</v>
+        <v>0.454642691985941</v>
       </c>
       <c r="H39">
-        <v>-0.4294388873820147</v>
+        <v>-0.4546426919859411</v>
       </c>
       <c r="I39">
-        <v>-0.8685606448478653</v>
+        <v>-0.9080778169460825</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
@@ -1903,22 +1903,22 @@
         <v>0.8397473563905411</v>
       </c>
       <c r="D40">
-        <v>0.4596303634237808</v>
+        <v>0.3881366285386105</v>
       </c>
       <c r="E40">
         <v>0.821187593955504</v>
       </c>
       <c r="F40">
-        <v>0.4410706009887436</v>
+        <v>0.3695768661035733</v>
       </c>
       <c r="G40">
-        <v>0.3801169929667603</v>
+        <v>0.4516107278519306</v>
       </c>
       <c r="H40">
-        <v>-0.3801169929667604</v>
+        <v>-0.4516107278519307</v>
       </c>
       <c r="I40">
-        <v>-0.4798057894098582</v>
+        <v>-0.5377620045074911</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
@@ -1941,22 +1941,22 @@
         <v>0.48</v>
       </c>
       <c r="D41">
-        <v>0.4612244035664207</v>
+        <v>0.3855269040122699</v>
       </c>
       <c r="E41">
         <v>0.6096176279974082</v>
       </c>
       <c r="F41">
-        <v>0.5908420315638289</v>
+        <v>0.5151445320096781</v>
       </c>
       <c r="G41">
-        <v>0.01877559643357929</v>
+        <v>0.09447309598773007</v>
       </c>
       <c r="H41">
-        <v>-0.01877559643357929</v>
+        <v>-0.09447309598773002</v>
       </c>
       <c r="I41">
-        <v>-0.02253934610271374</v>
+        <v>-0.106259763505716</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -1979,22 +1979,22 @@
         <v>0.502083469095723</v>
       </c>
       <c r="D42">
-        <v>0.4604664292505939</v>
+        <v>0.3474501014634773</v>
       </c>
       <c r="E42">
         <v>0.7891470860972862</v>
       </c>
       <c r="F42">
-        <v>0.747530046252157</v>
+        <v>0.6345137184650405</v>
       </c>
       <c r="G42">
-        <v>0.0416170398451291</v>
+        <v>0.1546333676322457</v>
       </c>
       <c r="H42">
-        <v>-0.04161703984512921</v>
+        <v>-0.1546333676322458</v>
       </c>
       <c r="I42">
-        <v>-0.06395195344608562</v>
+        <v>-0.220145464575505</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -2017,22 +2017,22 @@
         <v>0.5263959846508897</v>
       </c>
       <c r="D43">
-        <v>0.4577744555629211</v>
+        <v>0.3623281986403278</v>
       </c>
       <c r="E43">
         <v>0.312800145126382</v>
       </c>
       <c r="F43">
-        <v>0.2441786160384135</v>
+        <v>0.1487323591158202</v>
       </c>
       <c r="G43">
-        <v>0.06862152908796854</v>
+        <v>0.1640677860105619</v>
       </c>
       <c r="H43">
-        <v>-0.06862152908796854</v>
+        <v>-0.1640677860105619</v>
       </c>
       <c r="I43">
-        <v>-0.03822073426065069</v>
+        <v>-0.07572261614292837</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -2055,22 +2055,22 @@
         <v>0.46</v>
       </c>
       <c r="D44">
-        <v>0.4534819918361149</v>
+        <v>0.2995996442486632</v>
       </c>
       <c r="E44">
         <v>0.5267620410109616</v>
       </c>
       <c r="F44">
-        <v>0.5202440328470764</v>
+        <v>0.3663616852596248</v>
       </c>
       <c r="G44">
-        <v>0.006518008163885147</v>
+        <v>0.1604003557513368</v>
       </c>
       <c r="H44">
-        <v>-0.006518008163885147</v>
+        <v>-0.1604003557513368</v>
       </c>
       <c r="I44">
-        <v>-0.006824394137043999</v>
+        <v>-0.1432573634237616</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
@@ -2093,22 +2093,22 @@
         <v>0.5031808943414688</v>
       </c>
       <c r="D45">
-        <v>0.4538418986899065</v>
+        <v>0.2936142920210401</v>
       </c>
       <c r="E45">
         <v>0.3979680775074187</v>
       </c>
       <c r="F45">
-        <v>0.3486290818558564</v>
+        <v>0.18840147518699</v>
       </c>
       <c r="G45">
-        <v>0.04933899565156236</v>
+        <v>0.2095666023204287</v>
       </c>
       <c r="H45">
-        <v>-0.04933899565156236</v>
+        <v>-0.2095666023204287</v>
       </c>
       <c r="I45">
-        <v>-0.03683635399929344</v>
+        <v>-0.1228834748623168</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -2131,31 +2131,31 @@
         <v>0.4401293578968364</v>
       </c>
       <c r="D46">
-        <v>0.452245289381935</v>
+        <v>0.289106542847739</v>
       </c>
       <c r="E46">
         <v>0.6407790808091178</v>
       </c>
       <c r="F46">
-        <v>0.6528950122942163</v>
+        <v>0.4897562657600204</v>
       </c>
       <c r="G46">
-        <v>-0.0121159314850986</v>
+        <v>0.1510228150490974</v>
       </c>
       <c r="H46">
-        <v>0.01211593148509849</v>
+        <v>-0.1510228150490974</v>
       </c>
       <c r="I46">
-        <v>0.0156740666760869</v>
+        <v>-0.1707366305513782</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2169,28 +2169,28 @@
         <v>0.4438035404671155</v>
       </c>
       <c r="D47">
-        <v>0.4495094108685699</v>
+        <v>0.2907483809139259</v>
       </c>
       <c r="E47">
         <v>0.03212331069211072</v>
       </c>
       <c r="F47">
-        <v>0.03782918109356509</v>
+        <v>-0.1209318488610789</v>
       </c>
       <c r="G47">
-        <v>-0.005705870401454372</v>
+        <v>0.1530551595531896</v>
       </c>
       <c r="H47">
-        <v>0.005705870401454372</v>
+        <v>0.08880853816896817</v>
       </c>
       <c r="I47">
-        <v>0.0003991398523878675</v>
+        <v>0.01359260497913695</v>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2207,31 +2207,31 @@
         <v>0.39</v>
       </c>
       <c r="D48">
-        <v>0.4477724596020129</v>
+        <v>0.2564355480731927</v>
       </c>
       <c r="E48">
         <v>0.6666911554241067</v>
       </c>
       <c r="F48">
-        <v>0.7244636150261197</v>
+        <v>0.5331267034972994</v>
       </c>
       <c r="G48">
-        <v>-0.05777245960201288</v>
+        <v>0.1335644519268073</v>
       </c>
       <c r="H48">
-        <v>0.05777245960201294</v>
+        <v>-0.1335644519268073</v>
       </c>
       <c r="I48">
-        <v>0.08037043277598332</v>
+        <v>-0.160253014738833</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2245,31 +2245,31 @@
         <v>0.4476495795507702</v>
       </c>
       <c r="D49">
-        <v>0.4504538322865494</v>
+        <v>0.2766837437271186</v>
       </c>
       <c r="E49">
         <v>0.4476495795507702</v>
       </c>
       <c r="F49">
-        <v>0.4504538322865494</v>
+        <v>0.2766837437271186</v>
       </c>
       <c r="G49">
-        <v>-0.002804252735779167</v>
+        <v>0.1709658358236516</v>
       </c>
       <c r="H49">
-        <v>0.002804252735779167</v>
+        <v>-0.1709658358236516</v>
       </c>
       <c r="I49">
-        <v>0.002518508949657411</v>
+        <v>-0.1238362520291275</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
